--- a/MarsOnboradingIC.xlsx
+++ b/MarsOnboradingIC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/adedb4719efe1d1b/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shalu\source\repos\TASK1\TASK1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{B6898394-1932-4B2C-8AB3-E8C2B36C0FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46DFD1B3-C9BE-4ED7-9272-D3D296C88432}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206ABD2C-C5B4-4547-8570-61E1B7FC186B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{71EE54C5-580E-4F7E-8B88-1E54E23312FD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="123">
   <si>
     <t>Test Scenario ID</t>
   </si>
@@ -235,9 +235,6 @@
 5.User should be able to click on add button</t>
   </si>
   <si>
-    <t>User should see the message as Language Added</t>
-  </si>
-  <si>
     <t>User should see the message as Skill Added</t>
   </si>
   <si>
@@ -374,12 +371,6 @@
 5.User should be able to click on add button</t>
   </si>
   <si>
-    <t>TC_004:Check if user can add only Language</t>
-  </si>
-  <si>
-    <t>TC_005:Check if user can choose only Language level</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.User must logged in to acces the profile page
 2.Click on the Language/Skill tab
 </t>
@@ -427,40 +418,10 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>TC_006:Check if user can add more than 4 langugae to the list</t>
-  </si>
-  <si>
-    <t>TC_007:Check if user can edit the exisiting language</t>
-  </si>
-  <si>
-    <t>TC_008:Check if user can clcik the update button without editing</t>
-  </si>
-  <si>
-    <t>TC_009Check if user can delete the language</t>
-  </si>
-  <si>
-    <t>TC_010:Check if user can add a new Skill</t>
-  </si>
-  <si>
-    <t>TC_011:Check if user can add a already existing Skill</t>
-  </si>
-  <si>
-    <t>TC_0012:Check if user can use special characters in name</t>
-  </si>
-  <si>
-    <t>TC_013:Check if user can add only Skill</t>
-  </si>
-  <si>
     <t>fail</t>
   </si>
   <si>
-    <t>TC_014:Check if user can choose only Skill level</t>
-  </si>
-  <si>
     <t>Validate if user can add more than 4 Skills to the list</t>
-  </si>
-  <si>
-    <t>TC_015:Check if user can add more than 4 langugae to the list</t>
   </si>
   <si>
     <t>1.User must logged in to acces the profile page
@@ -477,16 +438,77 @@
     <t>User not able to  add the sKill</t>
   </si>
   <si>
-    <t>TC_016:Check if user can edit the exisiting Skill</t>
-  </si>
-  <si>
-    <t>TC_017:Check if user can click the update button without editing</t>
-  </si>
-  <si>
-    <t>TC_018:Check if user can delete the Skill</t>
-  </si>
-  <si>
-    <t>TC_019:Check if user can use cancel button to stop the add/edit operation</t>
+    <t>Validate if user can add Numerical Characters in language name</t>
+  </si>
+  <si>
+    <t>1.http://localhost:5003/Account/Profile
+2.Enter 12345 as language
+3.Select Fluent from Language level</t>
+  </si>
+  <si>
+    <t>User should see the message as "Language Added"</t>
+  </si>
+  <si>
+    <t>Validate if user can add Numerical Characters in Skill name</t>
+  </si>
+  <si>
+    <t>1.http://localhost:5003/Account/Profile
+2.Enter 35668 as Skill
+3.Select Fluent from Skill level</t>
+  </si>
+  <si>
+    <t>TC_004:Check if user can use special characters in name</t>
+  </si>
+  <si>
+    <t>TC_005:Check if user can add only Language</t>
+  </si>
+  <si>
+    <t>TC_006:Check if user can choose only Language level</t>
+  </si>
+  <si>
+    <t>TC_007:Check if user can add more than 4 langugae to the list</t>
+  </si>
+  <si>
+    <t>TC_008:Check if user can edit the exisiting language</t>
+  </si>
+  <si>
+    <t>TC_009:Check if user can clcik the update button without editing</t>
+  </si>
+  <si>
+    <t>TC_010:Check if user can delete the language</t>
+  </si>
+  <si>
+    <t>TC_011:Check if user can add a new Skill</t>
+  </si>
+  <si>
+    <t>TC_012:Check if user can add a already existing Skill</t>
+  </si>
+  <si>
+    <t>TC_0013:Check if user can use special characters in name</t>
+  </si>
+  <si>
+    <t>TC_0014:Check if user can use special characters in name</t>
+  </si>
+  <si>
+    <t>TC_015:Check if user can add only Skill</t>
+  </si>
+  <si>
+    <t>TC_016:Check if user can choose only Skill level</t>
+  </si>
+  <si>
+    <t>TC_017:Check if user can add more than 4 langugae to the list</t>
+  </si>
+  <si>
+    <t>TC_018:Check if user can edit the exisiting Skill</t>
+  </si>
+  <si>
+    <t>TC_019:Check if user can click the update button without editing</t>
+  </si>
+  <si>
+    <t>TC_020:Check if user can delete the Skill</t>
+  </si>
+  <si>
+    <t>TC_021:Check if user can use cancel button to stop the add/edit operation</t>
   </si>
 </sst>
 </file>
@@ -935,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A089CC57-285D-478C-B445-050C5BE8A46D}">
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.81640625" style="5" customWidth="1"/>
@@ -1012,7 +1034,7 @@
         <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>14</v>
@@ -1024,10 +1046,10 @@
         <v>46</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="116" x14ac:dyDescent="0.35">
@@ -1039,7 +1061,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>14</v>
@@ -1054,244 +1076,247 @@
         <v>19</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="116" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="116" x14ac:dyDescent="0.35">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="101.5" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" s="3" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A6" s="7"/>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="J6" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="7"/>
+      <c r="B8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="G8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="3" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="C9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="87" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="3" t="s">
+      <c r="J9" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="87" x14ac:dyDescent="0.35">
+      <c r="A10" s="7"/>
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="C10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="116" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>67</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="116" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>48</v>
@@ -1300,243 +1325,303 @@
         <v>49</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
       <c r="B13" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="87" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="3" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
       <c r="B15" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="87" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
       <c r="B16" s="3" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="A17" s="7"/>
       <c r="B17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="7"/>
+      <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="C20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>96</v>
+      <c r="B22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="A9:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
